--- a/artfynd/A 97-2024 artfynd.xlsx
+++ b/artfynd/A 97-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 97-2024 artfynd.xlsx
+++ b/artfynd/A 97-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61564257</v>
+        <v>61564237</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647701.9247681535</v>
+        <v>647702</v>
       </c>
       <c r="R2" t="n">
-        <v>6548688.875182784</v>
+        <v>6548689</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -759,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-06-20</t>
+          <t>2016-09-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-06-21</t>
+          <t>2016-09-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +783,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>Mattias Stahre</t>
+          <t>Mattias Stare</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,42 +801,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61564260</v>
+        <v>61564240</v>
       </c>
       <c r="B3" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -860,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647701.9247681535</v>
+        <v>647702</v>
       </c>
       <c r="R3" t="n">
-        <v>6548688.875182784</v>
+        <v>6548689</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -890,22 +880,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-06-21</t>
+          <t>2016-09-13</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-06-22</t>
+          <t>2016-09-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +909,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>Mattias Stahre</t>
+          <t>Mattias Stare</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,15 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61564241</v>
+        <v>61564257</v>
       </c>
       <c r="B4" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,26 +938,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -991,10 +976,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647701.9247681535</v>
+        <v>647702</v>
       </c>
       <c r="R4" t="n">
-        <v>6548688.875182784</v>
+        <v>6548689</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1021,22 +1006,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-09-13</t>
+          <t>2016-06-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-09-14</t>
+          <t>2016-06-21</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1035,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>Mattias Stahre</t>
+          <t>Mattias Stare</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1068,15 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61564251</v>
+        <v>61564241</v>
       </c>
       <c r="B5" t="n">
-        <v>57498</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,26 +1064,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1122,10 +1102,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647701.9247681535</v>
+        <v>647702</v>
       </c>
       <c r="R5" t="n">
-        <v>6548688.875182784</v>
+        <v>6548689</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1152,22 +1132,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-07-19</t>
+          <t>2016-09-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-07-20</t>
+          <t>2016-09-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,7 +1161,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>Mattias Stahre</t>
+          <t>Mattias Stare</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1199,42 +1179,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61564240</v>
+        <v>61564238</v>
       </c>
       <c r="B6" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1253,10 +1228,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>647701.9247681535</v>
+        <v>647702</v>
       </c>
       <c r="R6" t="n">
-        <v>6548688.875182784</v>
+        <v>6548689</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1312,7 +1287,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>Mattias Stahre</t>
+          <t>Mattias Stare</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1330,15 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>61564254</v>
+        <v>61564250</v>
       </c>
       <c r="B7" t="n">
-        <v>57505</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,10 +1354,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>647701.9247681535</v>
+        <v>647702</v>
       </c>
       <c r="R7" t="n">
-        <v>6548688.875182784</v>
+        <v>6548689</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1443,7 +1413,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>Mattias Stahre</t>
+          <t>Mattias Stare</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 97-2024 artfynd.xlsx
+++ b/artfynd/A 97-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61564237</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61564240</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61564257</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61564241</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1302,6 +1327,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61564238</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1428,8 +1458,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61564250</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>